--- a/week5/homework-svm-neural-net.xlsx
+++ b/week5/homework-svm-neural-net.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="131">
   <si>
     <t xml:space="preserve">[Description] SVMs &amp; a Neural Network Forward Pass</t>
   </si>
@@ -166,6 +166,9 @@
   </si>
   <si>
     <t xml:space="preserve">they would be the support vectors — answer like "c and d"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your Answer:</t>
   </si>
   <si>
     <t xml:space="preserve">[Description] STEP 2: hinge loss for five labelled points</t>
@@ -1054,7 +1057,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="8"/>
@@ -1188,20 +1191,22 @@
       <c r="A17" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="D17" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="11"/>
       <c r="E17" s="11"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="5" t="str">
-        <f aca="false">IF(F17="","",IF(UPPER(TRIM(F17))=UPPER("c and d"),"✓","✗"))</f>
+      <c r="F17" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="12"/>
+      <c r="H17" s="5" t="str">
+        <f aca="false">IF(G17="","",IF(UPPER(TRIM(G17))=UPPER("c and d"),"✓","✗"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="D17:E17"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:J17">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -1226,7 +1231,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="8"/>
@@ -1238,22 +1243,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1264,13 +1269,13 @@
         <v>37</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>40</v>
@@ -1346,7 +1351,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B14" s="7" t="n">
         <v>0</v>
@@ -1363,38 +1368,42 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="11"/>
+      <c r="D16" s="11" t="s">
+        <v>57</v>
+      </c>
       <c r="E16" s="11"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="5" t="str">
-        <f aca="false">IF(F16="","",IF(ROUND(F16,3)=ROUND(3,3),"✓","✗"))</f>
+      <c r="F16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="12"/>
+      <c r="H16" s="5" t="str">
+        <f aca="false">IF(G16="","",IF(ROUND(G16,3)=ROUND(3,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="11"/>
+      <c r="D18" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="E18" s="11"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="5" t="str">
-        <f aca="false">IF(F18="","",IF(UPPER(TRIM(F18))=UPPER("d"),"✓","✗"))</f>
+      <c r="F18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="12"/>
+      <c r="H18" s="5" t="str">
+        <f aca="false">IF(G18="","",IF(UPPER(TRIM(G18))=UPPER("d"),"✓","✗"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D18:E18"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:J18">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -1419,7 +1428,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -1430,38 +1439,38 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>40</v>
@@ -1469,7 +1478,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B12" s="7" t="n">
         <v>0</v>
@@ -1482,7 +1491,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="7" t="n">
         <v>1</v>
@@ -1495,7 +1504,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B14" s="7" t="n">
         <v>4</v>
@@ -1508,7 +1517,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B15" s="7" t="n">
         <v>9</v>
@@ -1521,38 +1530,42 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="11"/>
+      <c r="D17" s="11" t="s">
+        <v>73</v>
+      </c>
       <c r="E17" s="11"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="5" t="str">
-        <f aca="false">IF(F17="","",IF(ROUND(F17,3)=ROUND(0,3),"✓","✗"))</f>
+      <c r="F17" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="12"/>
+      <c r="H17" s="5" t="str">
+        <f aca="false">IF(G17="","",IF(ROUND(G17,3)=ROUND(0,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="11"/>
+      <c r="D19" s="11" t="s">
+        <v>75</v>
+      </c>
       <c r="E19" s="11"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="5" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))=UPPER("more"),"✓","✗"))</f>
+      <c r="F19" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G19" s="12"/>
+      <c r="H19" s="5" t="str">
+        <f aca="false">IF(G19="","",IF(UPPER(TRIM(G19))=UPPER("more"),"✓","✗"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D19:E19"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:J19">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -1588,41 +1601,41 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B10" s="7" t="n">
         <v>0</v>
@@ -1636,7 +1649,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B11" s="7" t="n">
         <v>-1</v>
@@ -1650,21 +1663,21 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B14" s="7" t="n">
         <v>1</v>
@@ -1678,7 +1691,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1689,19 +1702,19 @@
         <v>36</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H18" s="10" t="s">
         <v>40</v>
@@ -1760,38 +1773,42 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D23" s="11"/>
+      <c r="D23" s="11" t="s">
+        <v>95</v>
+      </c>
       <c r="E23" s="11"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="5" t="str">
-        <f aca="false">IF(F23="","",IF(ROUND(F23,3)=ROUND(9,3),"✓","✗"))</f>
+      <c r="F23" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G23" s="12"/>
+      <c r="H23" s="5" t="str">
+        <f aca="false">IF(G23="","",IF(ROUND(G23,3)=ROUND(9,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C25" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="D25" s="11"/>
+      <c r="D25" s="11" t="s">
+        <v>97</v>
+      </c>
       <c r="E25" s="11"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="5" t="str">
-        <f aca="false">IF(F25="","",IF(ROUND(F25,3)=ROUND(200960,3),"✓","✗"))</f>
+      <c r="F25" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G25" s="12"/>
+      <c r="H25" s="5" t="str">
+        <f aca="false">IF(G25="","",IF(ROUND(G25,3)=ROUND(200960,3),"✓","✗"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D25:E25"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:J25">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -1825,75 +1842,75 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B16" s="7" t="n">
         <v>3</v>
@@ -1901,7 +1918,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>44</v>
@@ -1909,20 +1926,20 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B22" s="7" t="n">
         <v>0</v>
@@ -1930,44 +1947,44 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B30" s="7" t="n">
         <v>9</v>
@@ -1975,7 +1992,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B31" s="7" t="n">
         <v>200960</v>
